--- a/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
+++ b/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7100" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7448" uniqueCount="1269">
   <si>
     <t>Result</t>
   </si>
@@ -3353,6 +3353,528 @@
   </si>
   <si>
     <t>Fri Jul 24 20:59:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:50:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:51:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:52:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:54:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:56:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 02:58:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:01:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:04:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:21:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:22:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:23:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:24:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:25:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:28:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:31:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:34:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:36:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:37:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:38:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:40:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:41:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:44:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:46:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 03:49:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:09:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:10:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:12:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:13:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:14:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:17:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:20:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:23:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:26:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:28:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:29:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:30:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:33:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:36:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:39:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:41:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:44:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:47:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:50:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:53:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:56:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 04:59:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:00:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:02:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:03:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:04:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:07:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:10:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 05:12:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:22:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:23:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:25:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:27:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:29:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:32:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:36:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:39:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:40:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:40:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:41:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:42:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:46:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:49:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:51:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:54:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:55:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:57:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 06:59:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:00:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:03:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:05:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:08:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:11:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:12:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:12:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:13:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:14:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:17:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:20:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 07:22:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:51:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:52:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:53:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:55:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 01:59:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:02:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:06:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:24:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:25:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:26:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:27:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:28:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:31:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:33:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:36:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:39:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:40:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:41:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:42:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:43:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:46:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:49:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 02:51:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:12:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:15:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:16:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:18:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:21:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:24:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:27:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:30:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:32:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:33:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:35:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:36:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:39:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:42:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:45:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:48:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:50:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:52:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:54:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:56:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 03:59:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:02:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:04:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:07:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:09:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:10:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:12:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:14:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:17:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:20:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 04:22:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:39:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:41:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:42:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:44:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:47:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:50:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:53:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:56:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:57:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:58:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 05:59:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:00:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:03:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:06:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:08:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:11:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:12:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:14:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:15:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:17:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:19:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:22:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:25:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:28:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:30:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:31:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:32:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:35:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:38:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 01 06:41:38 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3820,7 +4342,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1085</v>
+        <v>1214</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -3907,7 +4429,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1086</v>
+        <v>1215</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4090,7 +4612,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1072</v>
+        <v>1263</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>78</v>
@@ -4144,7 +4666,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1073</v>
+        <v>1264</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>78</v>
@@ -4297,7 +4819,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1074</v>
+        <v>1265</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>79</v>
@@ -4352,7 +4874,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1075</v>
+        <v>1266</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
@@ -4503,7 +5025,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>996</v>
+        <v>1192</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4589,7 +5111,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>997</v>
+        <v>1193</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -4774,7 +5296,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1076</v>
+        <v>1267</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>79</v>
@@ -4829,7 +5351,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1077</v>
+        <v>1268</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>79</v>
@@ -4983,7 +5505,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>988</v>
+        <v>1184</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5072,7 +5594,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>989</v>
+        <v>1185</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5263,7 +5785,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1004</v>
+        <v>1200</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5353,7 +5875,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1005</v>
+        <v>1201</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5545,10 +6067,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1000</v>
+        <v>1196</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5640,10 +6162,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1001</v>
+        <v>1197</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5849,10 +6371,10 @@
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1008</v>
+        <v>1204</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5948,10 +6470,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1009</v>
+        <v>1205</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6149,7 +6671,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>986</v>
+        <v>1182</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6238,7 +6760,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>987</v>
+        <v>1183</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -6432,10 +6954,10 @@
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>990</v>
+        <v>1186</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6530,10 +7052,10 @@
     </row>
     <row ht="72" r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>991</v>
+        <v>1187</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6747,10 +7269,10 @@
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>1089</v>
+        <v>1218</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6843,10 +7365,10 @@
     </row>
     <row ht="72" r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>1090</v>
+        <v>1219</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7047,10 +7569,10 @@
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>992</v>
+        <v>1188</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7145,10 +7667,10 @@
     </row>
     <row ht="72" r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>993</v>
+        <v>1189</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7348,7 +7870,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>994</v>
+        <v>1190</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7437,7 +7959,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>995</v>
+        <v>1191</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -7625,7 +8147,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1002</v>
+        <v>1198</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7715,7 +8237,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1003</v>
+        <v>1199</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -7907,10 +8429,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>998</v>
+        <v>1194</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8002,10 +8524,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>999</v>
+        <v>1195</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8212,10 +8734,10 @@
     </row>
     <row ht="72" r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1006</v>
+        <v>1202</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8312,10 +8834,10 @@
     </row>
     <row ht="72" r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1007</v>
+        <v>1203</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8522,10 +9044,10 @@
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1039</v>
+        <v>1236</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8619,10 +9141,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1040</v>
+        <v>1237</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8818,7 +9340,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1035</v>
+        <v>1232</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -8905,7 +9427,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1036</v>
+        <v>1233</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -9100,10 +9622,10 @@
     </row>
     <row ht="72" r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1037</v>
+        <v>1234</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9197,10 +9719,10 @@
     </row>
     <row ht="72" r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1038</v>
+        <v>1235</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9399,7 +9921,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1033</v>
+        <v>1230</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9487,7 +10009,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1034</v>
+        <v>1231</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9674,7 +10196,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1025</v>
+        <v>1222</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9755,7 +10277,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1026</v>
+        <v>1223</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9941,10 +10463,10 @@
     </row>
     <row ht="72" r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1091</v>
+        <v>1220</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10037,10 +10559,10 @@
     </row>
     <row ht="72" r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1092</v>
+        <v>1221</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10232,7 +10754,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1027</v>
+        <v>1224</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -10312,7 +10834,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1028</v>
+        <v>1225</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -10494,10 +11016,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1029</v>
+        <v>1226</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10583,10 +11105,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1030</v>
+        <v>1227</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10777,10 +11299,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1031</v>
+        <v>1228</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10866,10 +11388,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1032</v>
+        <v>1229</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11054,7 +11576,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1050</v>
+        <v>1247</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11136,7 +11658,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1051</v>
+        <v>1248</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11314,7 +11836,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1048</v>
+        <v>1245</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -11396,7 +11918,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1049</v>
+        <v>1246</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -11580,10 +12102,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1052</v>
+        <v>1249</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11671,10 +12193,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1053</v>
+        <v>1250</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11861,7 +12383,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1058</v>
+        <v>1255</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11943,7 +12465,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1059</v>
+        <v>1256</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -12121,7 +12643,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1056</v>
+        <v>1253</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -12203,7 +12725,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1057</v>
+        <v>1254</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -12387,10 +12909,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1062</v>
+        <v>1259</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12478,10 +13000,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1063</v>
+        <v>1260</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -12674,10 +13196,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1060</v>
+        <v>1257</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -12765,10 +13287,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1061</v>
+        <v>1258</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -12961,7 +13483,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>1094</v>
+        <v>1216</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -13048,7 +13570,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>1088</v>
+        <v>1217</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -13234,7 +13756,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1043</v>
+        <v>1240</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13494,7 +14016,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1041</v>
+        <v>1238</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -13576,7 +14098,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1042</v>
+        <v>1239</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -13760,10 +14282,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1044</v>
+        <v>1241</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -13851,10 +14373,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1045</v>
+        <v>1242</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14047,10 +14569,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1046</v>
+        <v>1243</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14138,10 +14660,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1047</v>
+        <v>1244</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14334,10 +14856,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1054</v>
+        <v>1251</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14425,10 +14947,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1055</v>
+        <v>1252</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14621,10 +15143,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>1093</v>
+        <v>1206</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -14704,7 +15226,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>863</v>
+        <v>1207</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -14880,7 +15402,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1079</v>
+        <v>1208</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -14960,7 +15482,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1080</v>
+        <v>1209</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -15142,10 +15664,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1081</v>
+        <v>1210</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -15231,10 +15753,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1082</v>
+        <v>1211</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -15425,10 +15947,10 @@
     </row>
     <row ht="72" r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1083</v>
+        <v>1212</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -15514,10 +16036,10 @@
     </row>
     <row ht="72" r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="0">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1084</v>
+        <v>1213</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -15702,7 +16224,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1064</v>
+        <v>1261</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>75</v>
@@ -15758,7 +16280,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1065</v>
+        <v>1262</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>75</v>

--- a/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
+++ b/KatalonData/IWPTestData/VRelay25PaymentsExtension.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7448" uniqueCount="1269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7560" uniqueCount="1325">
   <si>
     <t>Result</t>
   </si>
@@ -3875,6 +3875,174 @@
   </si>
   <si>
     <t>Thu Oct 01 06:41:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:56:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:58:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 09:59:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:01:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:03:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:05:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:09:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:12:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:32:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:33:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:34:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:35:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:36:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:39:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:45:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:48:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:49:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:50:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:52:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:54:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 10:57:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:00:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:03:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:25:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:27:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:29:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:30:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:32:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:35:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:38:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:41:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:44:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:45:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:47:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:48:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:50:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:53:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:55:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 11:58:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:01:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:03:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:04:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:06:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:09:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:12:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:15:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:18:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:21:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:23:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:25:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:26:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:28:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:31:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:35:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 12:38:24 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -4342,7 +4510,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1214</v>
+        <v>1301</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -4429,7 +4597,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1215</v>
+        <v>1302</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5025,7 +5193,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1192</v>
+        <v>1279</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5111,7 +5279,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1193</v>
+        <v>1280</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5505,7 +5673,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1184</v>
+        <v>1271</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5594,7 +5762,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1185</v>
+        <v>1272</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -5785,7 +5953,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1200</v>
+        <v>1287</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -5875,7 +6043,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1201</v>
+        <v>1288</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6070,7 +6238,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1196</v>
+        <v>1283</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6165,7 +6333,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1197</v>
+        <v>1284</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6374,7 +6542,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1204</v>
+        <v>1291</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -6473,7 +6641,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1205</v>
+        <v>1292</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -6671,7 +6839,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1182</v>
+        <v>1269</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6760,7 +6928,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1183</v>
+        <v>1270</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -6957,7 +7125,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1186</v>
+        <v>1273</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7055,7 +7223,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1187</v>
+        <v>1274</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7272,7 +7440,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>1218</v>
+        <v>1305</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7368,7 +7536,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>1219</v>
+        <v>1306</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7572,7 +7740,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1188</v>
+        <v>1275</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -7670,7 +7838,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1189</v>
+        <v>1276</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -7870,7 +8038,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1190</v>
+        <v>1277</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7959,7 +8127,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1191</v>
+        <v>1278</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -8147,7 +8315,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1198</v>
+        <v>1285</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -8237,7 +8405,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1199</v>
+        <v>1286</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -8432,7 +8600,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1194</v>
+        <v>1281</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8527,7 +8695,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1195</v>
+        <v>1282</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -8737,7 +8905,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1202</v>
+        <v>1289</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -8837,7 +9005,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1203</v>
+        <v>1290</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9047,7 +9215,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1236</v>
+        <v>1323</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9144,7 +9312,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1237</v>
+        <v>1324</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9340,7 +9508,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1232</v>
+        <v>1319</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -9427,7 +9595,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1233</v>
+        <v>1320</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -9625,7 +9793,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1234</v>
+        <v>1321</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -9722,7 +9890,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1235</v>
+        <v>1322</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -9921,7 +10089,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1230</v>
+        <v>1317</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10009,7 +10177,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1231</v>
+        <v>1318</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10196,7 +10364,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1222</v>
+        <v>1309</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10277,7 +10445,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1223</v>
+        <v>1310</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10466,7 +10634,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1220</v>
+        <v>1307</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -10562,7 +10730,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1221</v>
+        <v>1308</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -10754,7 +10922,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1224</v>
+        <v>1311</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -10834,7 +11002,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1225</v>
+        <v>1312</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -11019,7 +11187,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1226</v>
+        <v>1313</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11108,7 +11276,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1227</v>
+        <v>1314</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -11302,7 +11470,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1228</v>
+        <v>1315</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -11391,7 +11559,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1229</v>
+        <v>1316</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -13483,7 +13651,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>1216</v>
+        <v>1303</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -13570,7 +13738,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>1217</v>
+        <v>1304</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -15146,7 +15314,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>1206</v>
+        <v>1293</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -15223,10 +15391,10 @@
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s" s="2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>1207</v>
+        <v>1294</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -15402,7 +15570,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1208</v>
+        <v>1295</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -15482,7 +15650,7 @@
         <v>55</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1209</v>
+        <v>1296</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -15667,7 +15835,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1210</v>
+        <v>1297</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -15756,7 +15924,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1211</v>
+        <v>1298</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
@@ -15950,7 +16118,7 @@
         <v>70</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>1212</v>
+        <v>1299</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>56</v>
@@ -16039,7 +16207,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>1213</v>
+        <v>1300</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>56</v>
